--- a/data/services_transformes.xlsx
+++ b/data/services_transformes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SekouDRAME\Desktop\ANSD_KAFFRINE\Dashboard_SRSD_Kaffrine\dashboard_multi_sectoriel_kaffrine\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4121B97-1FB5-42A9-90A9-2E96F562C15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F34294-DC1D-402E-9FB1-6E9955009378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="17" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AGRICULTURE" sheetId="1" r:id="rId1"/>
@@ -37,6 +37,9 @@
     <sheet name="TRANSPORTS" sheetId="22" r:id="rId22"/>
     <sheet name="VULNERABILITE PROTECTION SOCIAL" sheetId="23" r:id="rId23"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">AQUACULTURE!$A$1:$P$34</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -56,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3700" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3698" uniqueCount="491">
   <si>
     <t>secteur</t>
   </si>
@@ -24151,8 +24154,8 @@
       <c r="M11">
         <v>0</v>
       </c>
-      <c r="N11" t="s">
-        <v>77</v>
+      <c r="N11">
+        <v>0</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -24201,8 +24204,8 @@
       <c r="M12">
         <v>0</v>
       </c>
-      <c r="N12" t="s">
-        <v>77</v>
+      <c r="N12">
+        <v>0</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -25312,6 +25315,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P34" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
